--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30210"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EDA394C-4482-4B0D-87F5-0EFD141B4EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B02B326A-95E1-44D3-816A-DFC671206AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="15" windowWidth="18960" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -647,7 +647,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -669,6 +669,66 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -678,71 +738,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1051,238 +1048,238 @@
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.1640625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="63.5" style="15" customWidth="1"/>
-    <col min="3" max="3" width="17.5" style="15" customWidth="1"/>
+    <col min="1" max="1" width="27.1640625" customWidth="1"/>
+    <col min="2" max="2" width="63.5" customWidth="1"/>
+    <col min="3" max="3" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="34.5" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="28"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="19"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="19"/>
     </row>
     <row r="3" spans="1:3" ht="19.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="29"/>
+      <c r="C3" s="30"/>
     </row>
     <row r="4" spans="1:3" ht="19.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="29"/>
+      <c r="C4" s="30"/>
     </row>
     <row r="5" spans="1:3" ht="19.5" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="29"/>
+      <c r="C5" s="30"/>
     </row>
     <row r="6" spans="1:3" ht="19.5" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="17">
-        <v>46172</v>
-      </c>
-      <c r="C6" s="29"/>
+      <c r="B6" s="8">
+        <v>46187</v>
+      </c>
+      <c r="C6" s="30"/>
     </row>
     <row r="7" spans="1:3" ht="26.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="28"/>
+      <c r="C7" s="19"/>
     </row>
     <row r="8" spans="1:3" ht="14.45" customHeight="1">
       <c r="A8" s="2"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="30"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="20"/>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
       <c r="A9" s="4"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="30"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="20"/>
     </row>
     <row r="10" spans="1:3" ht="28.35" customHeight="1">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="28"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="19"/>
     </row>
     <row r="11" spans="1:3" ht="24" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="28"/>
+      <c r="C11" s="19"/>
     </row>
     <row r="12" spans="1:3" ht="27.75" customHeight="1">
       <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="12">
         <v>73</v>
       </c>
-      <c r="C12" s="28"/>
+      <c r="C12" s="19"/>
     </row>
     <row r="13" spans="1:3" ht="29.25" customHeight="1">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="22">
-        <v>37</v>
-      </c>
-      <c r="C13" s="28"/>
+      <c r="B13" s="13">
+        <v>39</v>
+      </c>
+      <c r="C13" s="19"/>
     </row>
     <row r="14" spans="1:3" ht="30.75" customHeight="1">
       <c r="A14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="23">
-        <v>36</v>
-      </c>
-      <c r="C14" s="28"/>
+      <c r="B14" s="14">
+        <v>34</v>
+      </c>
+      <c r="C14" s="19"/>
     </row>
     <row r="15" spans="1:3" ht="21" customHeight="1">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="24">
-        <v>0.50680000000000003</v>
-      </c>
-      <c r="C15" s="30"/>
+      <c r="B15" s="15">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="C15" s="20"/>
     </row>
     <row r="16" spans="1:3" ht="22.5" customHeight="1">
       <c r="A16" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="24">
-        <v>0.49320000000000003</v>
-      </c>
-      <c r="C16" s="28"/>
+      <c r="B16" s="15">
+        <v>0.4657</v>
+      </c>
+      <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:3" ht="14.45" customHeight="1">
       <c r="A17" s="3"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="30"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="20"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1">
       <c r="A18" s="4"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="30"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="20"/>
     </row>
     <row r="19" spans="1:3" ht="18.75" customHeight="1">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="30"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="20"/>
     </row>
     <row r="20" spans="1:3" ht="31.5" customHeight="1">
       <c r="A20" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="21">
-        <v>36</v>
-      </c>
-      <c r="C20" s="28"/>
+      <c r="B20" s="12">
+        <v>34</v>
+      </c>
+      <c r="C20" s="19"/>
     </row>
     <row r="21" spans="1:3" ht="42" customHeight="1">
       <c r="A21" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="26">
-        <v>29</v>
-      </c>
-      <c r="C21" s="28"/>
+      <c r="B21" s="17">
+        <v>27</v>
+      </c>
+      <c r="C21" s="19"/>
     </row>
     <row r="22" spans="1:3" ht="41.25" customHeight="1">
       <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="18">
         <v>7</v>
       </c>
-      <c r="C22" s="28"/>
+      <c r="C22" s="19"/>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1">
       <c r="A23" s="3"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="30"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="20"/>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1">
       <c r="A24" s="4"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="30"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="20"/>
     </row>
     <row r="25" spans="1:3" ht="30" customHeight="1">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="28"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="19"/>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="30"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="20"/>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="30"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="20"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="30"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="20"/>
     </row>
     <row r="29" spans="1:3" ht="32.25" customHeight="1">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="28"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="19"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="31"/>
-      <c r="B30" s="31"/>
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A26:B29"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
